--- a/output/yearly_total_coral_cover_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_66_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.24924100150402</v>
+        <v>1.250301289024606</v>
       </c>
       <c r="C3" t="n">
-        <v>4.605090719604604</v>
+        <v>4.670357306982932</v>
       </c>
       <c r="D3" t="n">
-        <v>6.06545830400489</v>
+        <v>6.054138752974924</v>
       </c>
       <c r="E3" t="n">
-        <v>11.91979002511351</v>
+        <v>11.97479734898246</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.367065686190794</v>
+        <v>1.370492346931609</v>
       </c>
       <c r="C4" t="n">
-        <v>5.055864903698471</v>
+        <v>5.24971056917308</v>
       </c>
       <c r="D4" t="n">
-        <v>6.310975312986821</v>
+        <v>6.240357088123402</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73390590287609</v>
+        <v>12.86056000422809</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.526802199793332</v>
+        <v>1.534807705000507</v>
       </c>
       <c r="C5" t="n">
-        <v>5.623262908408855</v>
+        <v>5.990300144132875</v>
       </c>
       <c r="D5" t="n">
-        <v>6.626452968311743</v>
+        <v>6.502146521268506</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77651807651393</v>
+        <v>14.02725437040189</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.701673054566852</v>
+        <v>1.715565844415468</v>
       </c>
       <c r="C6" t="n">
-        <v>6.351891580558353</v>
+        <v>6.874699314756063</v>
       </c>
       <c r="D6" t="n">
-        <v>6.990821180814697</v>
+        <v>6.807689227257666</v>
       </c>
       <c r="E6" t="n">
-        <v>15.0443858159399</v>
+        <v>15.3979543864292</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.902466478690165</v>
+        <v>1.93370712389235</v>
       </c>
       <c r="C7" t="n">
-        <v>7.259577934442096</v>
+        <v>7.883665600345426</v>
       </c>
       <c r="D7" t="n">
-        <v>7.371203064938634</v>
+        <v>7.155018091475583</v>
       </c>
       <c r="E7" t="n">
-        <v>16.5332474780709</v>
+        <v>16.97239081571336</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.143361453849974</v>
+        <v>1.181189003913944</v>
       </c>
       <c r="C8" t="n">
-        <v>5.008295226487274</v>
+        <v>5.457297779223092</v>
       </c>
       <c r="D8" t="n">
-        <v>5.752230436927845</v>
+        <v>5.336750508016579</v>
       </c>
       <c r="E8" t="n">
-        <v>11.90388711726509</v>
+        <v>11.97523729115361</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.418373313235774</v>
+        <v>1.494647097719815</v>
       </c>
       <c r="C9" t="n">
-        <v>6.227919666201464</v>
+        <v>6.693423025922396</v>
       </c>
       <c r="D9" t="n">
-        <v>6.343623211795347</v>
+        <v>5.709282011400671</v>
       </c>
       <c r="E9" t="n">
-        <v>13.98991619123258</v>
+        <v>13.89735213504288</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.704214645910488</v>
+        <v>1.837396353970371</v>
       </c>
       <c r="C10" t="n">
-        <v>7.617353357703688</v>
+        <v>8.076567179623622</v>
       </c>
       <c r="D10" t="n">
-        <v>6.885613957045006</v>
+        <v>6.198074219308642</v>
       </c>
       <c r="E10" t="n">
-        <v>16.20718196065918</v>
+        <v>16.11203775290263</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.979002430732349</v>
+        <v>2.178958801735982</v>
       </c>
       <c r="C11" t="n">
-        <v>9.11058699337045</v>
+        <v>9.576630202570469</v>
       </c>
       <c r="D11" t="n">
-        <v>7.427178834713588</v>
+        <v>6.728294117734754</v>
       </c>
       <c r="E11" t="n">
-        <v>18.51676825881639</v>
+        <v>18.48388312204121</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.259695472955787</v>
+        <v>2.515612545851063</v>
       </c>
       <c r="C12" t="n">
-        <v>10.65932550874811</v>
+        <v>11.13565072532842</v>
       </c>
       <c r="D12" t="n">
-        <v>7.931695442379248</v>
+        <v>7.190702942442936</v>
       </c>
       <c r="E12" t="n">
-        <v>20.85071642408315</v>
+        <v>20.84196621362242</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.536034321462828</v>
+        <v>2.83534402328505</v>
       </c>
       <c r="C13" t="n">
-        <v>12.33246533002725</v>
+        <v>12.76990409775296</v>
       </c>
       <c r="D13" t="n">
-        <v>8.488445515941516</v>
+        <v>7.666407049052977</v>
       </c>
       <c r="E13" t="n">
-        <v>23.3569451674316</v>
+        <v>23.27165517009099</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.471414006693992</v>
+        <v>1.620993086913036</v>
       </c>
       <c r="C14" t="n">
-        <v>8.610153168216504</v>
+        <v>9.014976834062676</v>
       </c>
       <c r="D14" t="n">
-        <v>6.449846797452525</v>
+        <v>5.875563660376311</v>
       </c>
       <c r="E14" t="n">
-        <v>16.53141397236302</v>
+        <v>16.51153358135202</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.486474016477138</v>
+        <v>1.652340291109637</v>
       </c>
       <c r="C15" t="n">
-        <v>9.382003213295347</v>
+        <v>9.694140078383576</v>
       </c>
       <c r="D15" t="n">
-        <v>6.503676024076378</v>
+        <v>5.900490234587137</v>
       </c>
       <c r="E15" t="n">
-        <v>17.37215325384886</v>
+        <v>17.24697060408035</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.713414815790831</v>
+        <v>1.917529980980785</v>
       </c>
       <c r="C16" t="n">
-        <v>11.13790806972598</v>
+        <v>11.41689131484179</v>
       </c>
       <c r="D16" t="n">
-        <v>7.072628271118533</v>
+        <v>6.370187788729939</v>
       </c>
       <c r="E16" t="n">
-        <v>19.92395115663534</v>
+        <v>19.70460908455252</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.366769518898324</v>
+        <v>1.543258303690774</v>
       </c>
       <c r="C17" t="n">
-        <v>10.33270805513387</v>
+        <v>10.43973818985086</v>
       </c>
       <c r="D17" t="n">
-        <v>6.602842359682349</v>
+        <v>5.910857490343984</v>
       </c>
       <c r="E17" t="n">
-        <v>18.30231993371455</v>
+        <v>17.89385398388562</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.551593341699829</v>
+        <v>1.768284694981185</v>
       </c>
       <c r="C18" t="n">
-        <v>12.07439720480701</v>
+        <v>12.16166475823751</v>
       </c>
       <c r="D18" t="n">
-        <v>7.086745803105601</v>
+        <v>6.308583120288452</v>
       </c>
       <c r="E18" t="n">
-        <v>20.71273634961244</v>
+        <v>20.23853257350715</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.547165659553676</v>
+        <v>1.780144207248487</v>
       </c>
       <c r="C19" t="n">
-        <v>12.91496958918313</v>
+        <v>12.97869483266579</v>
       </c>
       <c r="D19" t="n">
-        <v>7.220823087074587</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="E19" t="n">
-        <v>21.6829583358114</v>
+        <v>21.17946902568842</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.715329223814112</v>
+        <v>1.98373904615519</v>
       </c>
       <c r="C20" t="n">
-        <v>14.76070436055234</v>
+        <v>14.85322426420056</v>
       </c>
       <c r="D20" t="n">
-        <v>7.709291657322589</v>
+        <v>6.876907048799888</v>
       </c>
       <c r="E20" t="n">
-        <v>24.18532524168904</v>
+        <v>23.71387035915564</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.020183126868073</v>
+        <v>1.181219202795677</v>
       </c>
       <c r="C21" t="n">
-        <v>10.76821133673776</v>
+        <v>10.88641376032907</v>
       </c>
       <c r="D21" t="n">
-        <v>6.464641735355524</v>
+        <v>5.758519699076007</v>
       </c>
       <c r="E21" t="n">
-        <v>18.25303619896136</v>
+        <v>17.82615266220076</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_66_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250301289024606</v>
+        <v>1.253236714660305</v>
       </c>
       <c r="C3" t="n">
-        <v>4.670357306982932</v>
+        <v>4.585190693639523</v>
       </c>
       <c r="D3" t="n">
-        <v>6.054138752974924</v>
+        <v>6.058105013700082</v>
       </c>
       <c r="E3" t="n">
-        <v>11.97479734898246</v>
+        <v>11.89653242199991</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370492346931609</v>
+        <v>1.370260371152803</v>
       </c>
       <c r="C4" t="n">
-        <v>5.24971056917308</v>
+        <v>5.0062585241997</v>
       </c>
       <c r="D4" t="n">
-        <v>6.240357088123402</v>
+        <v>6.370832941682186</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86056000422809</v>
+        <v>12.74735183703469</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.534807705000507</v>
+        <v>1.528178664797597</v>
       </c>
       <c r="C5" t="n">
-        <v>5.990300144132875</v>
+        <v>5.531500392549645</v>
       </c>
       <c r="D5" t="n">
-        <v>6.502146521268506</v>
+        <v>6.74184801835698</v>
       </c>
       <c r="E5" t="n">
-        <v>14.02725437040189</v>
+        <v>13.80152707570422</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.715565844415468</v>
+        <v>1.709102092372582</v>
       </c>
       <c r="C6" t="n">
-        <v>6.874699314756063</v>
+        <v>6.196346076127521</v>
       </c>
       <c r="D6" t="n">
-        <v>6.807689227257666</v>
+        <v>7.178756306144038</v>
       </c>
       <c r="E6" t="n">
-        <v>15.3979543864292</v>
+        <v>15.08420447464414</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.93370712389235</v>
+        <v>1.912105928031676</v>
       </c>
       <c r="C7" t="n">
-        <v>7.883665600345426</v>
+        <v>6.985735155778724</v>
       </c>
       <c r="D7" t="n">
-        <v>7.155018091475583</v>
+        <v>7.646333618828572</v>
       </c>
       <c r="E7" t="n">
-        <v>16.97239081571336</v>
+        <v>16.54417470263897</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.181189003913944</v>
+        <v>1.151750244036773</v>
       </c>
       <c r="C8" t="n">
-        <v>5.457297779223092</v>
+        <v>4.679037462404898</v>
       </c>
       <c r="D8" t="n">
-        <v>5.336750508016579</v>
+        <v>5.940221440300684</v>
       </c>
       <c r="E8" t="n">
-        <v>11.97523729115361</v>
+        <v>11.77100914674235</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.494647097719815</v>
+        <v>1.432870871693193</v>
       </c>
       <c r="C9" t="n">
-        <v>6.693423025922396</v>
+        <v>5.707449632761601</v>
       </c>
       <c r="D9" t="n">
-        <v>5.709282011400671</v>
+        <v>6.622475104282461</v>
       </c>
       <c r="E9" t="n">
-        <v>13.89735213504288</v>
+        <v>13.76279560873725</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.837396353970371</v>
+        <v>1.732525673525589</v>
       </c>
       <c r="C10" t="n">
-        <v>8.076567179623622</v>
+        <v>6.865718873476133</v>
       </c>
       <c r="D10" t="n">
-        <v>6.198074219308642</v>
+        <v>7.256113146975334</v>
       </c>
       <c r="E10" t="n">
-        <v>16.11203775290263</v>
+        <v>15.85435769397706</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.178958801735982</v>
+        <v>2.046200692304561</v>
       </c>
       <c r="C11" t="n">
-        <v>9.576630202570469</v>
+        <v>8.091538219934264</v>
       </c>
       <c r="D11" t="n">
-        <v>6.728294117734754</v>
+        <v>7.907248342839601</v>
       </c>
       <c r="E11" t="n">
-        <v>18.48388312204121</v>
+        <v>18.04498725507843</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.515612545851063</v>
+        <v>2.366741706763884</v>
       </c>
       <c r="C12" t="n">
-        <v>11.13565072532842</v>
+        <v>9.377056087330072</v>
       </c>
       <c r="D12" t="n">
-        <v>7.190702942442936</v>
+        <v>8.529649005514655</v>
       </c>
       <c r="E12" t="n">
-        <v>20.84196621362242</v>
+        <v>20.27344679960861</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.83534402328505</v>
+        <v>2.678193518126936</v>
       </c>
       <c r="C13" t="n">
-        <v>12.76990409775296</v>
+        <v>10.70000347509128</v>
       </c>
       <c r="D13" t="n">
-        <v>7.666407049052977</v>
+        <v>9.090164065741256</v>
       </c>
       <c r="E13" t="n">
-        <v>23.27165517009099</v>
+        <v>22.46836105895947</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.620993086913036</v>
+        <v>1.550474149316988</v>
       </c>
       <c r="C14" t="n">
-        <v>9.014976834062676</v>
+        <v>7.508838411069475</v>
       </c>
       <c r="D14" t="n">
-        <v>5.875563660376311</v>
+        <v>6.914449081010286</v>
       </c>
       <c r="E14" t="n">
-        <v>16.51153358135202</v>
+        <v>15.97376164139675</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.652340291109637</v>
+        <v>1.587643117399772</v>
       </c>
       <c r="C15" t="n">
-        <v>9.694140078383576</v>
+        <v>7.978958116725103</v>
       </c>
       <c r="D15" t="n">
-        <v>5.900490234587137</v>
+        <v>7.012103525151717</v>
       </c>
       <c r="E15" t="n">
-        <v>17.24697060408035</v>
+        <v>16.57870475927659</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.917529980980785</v>
+        <v>1.847973156134899</v>
       </c>
       <c r="C16" t="n">
-        <v>11.41689131484179</v>
+        <v>9.333819035970912</v>
       </c>
       <c r="D16" t="n">
-        <v>6.370187788729939</v>
+        <v>7.590971424006763</v>
       </c>
       <c r="E16" t="n">
-        <v>19.70460908455252</v>
+        <v>18.77276361611257</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.543258303690774</v>
+        <v>1.485570808589231</v>
       </c>
       <c r="C17" t="n">
-        <v>10.43973818985086</v>
+        <v>8.573052922473018</v>
       </c>
       <c r="D17" t="n">
-        <v>5.910857490343984</v>
+        <v>7.131464411034043</v>
       </c>
       <c r="E17" t="n">
-        <v>17.89385398388562</v>
+        <v>17.19008814209629</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.768284694981185</v>
+        <v>1.700229944122797</v>
       </c>
       <c r="C18" t="n">
-        <v>12.16166475823751</v>
+        <v>9.955510769685205</v>
       </c>
       <c r="D18" t="n">
-        <v>6.308583120288452</v>
+        <v>7.715957724234424</v>
       </c>
       <c r="E18" t="n">
-        <v>20.23853257350715</v>
+        <v>19.37169843804243</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.780144207248487</v>
+        <v>1.714200213954229</v>
       </c>
       <c r="C19" t="n">
-        <v>12.97869483266579</v>
+        <v>10.61033648841783</v>
       </c>
       <c r="D19" t="n">
-        <v>6.42062998577414</v>
+        <v>7.895362299708487</v>
       </c>
       <c r="E19" t="n">
-        <v>21.17946902568842</v>
+        <v>20.21989900208055</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.98373904615519</v>
+        <v>1.919149864692792</v>
       </c>
       <c r="C20" t="n">
-        <v>14.85322426420056</v>
+        <v>12.2394289938909</v>
       </c>
       <c r="D20" t="n">
-        <v>6.876907048799888</v>
+        <v>8.450020300176806</v>
       </c>
       <c r="E20" t="n">
-        <v>23.71387035915564</v>
+        <v>22.6085991587605</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.181219202795677</v>
+        <v>1.146671501083232</v>
       </c>
       <c r="C21" t="n">
-        <v>10.88641376032907</v>
+        <v>9.071309517332358</v>
       </c>
       <c r="D21" t="n">
-        <v>5.758519699076007</v>
+        <v>7.092400669882062</v>
       </c>
       <c r="E21" t="n">
-        <v>17.82615266220076</v>
+        <v>17.31038168829765</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_66_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_66_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253236714660305</v>
+        <v>2.618458093788368</v>
       </c>
       <c r="C3" t="n">
-        <v>4.585190693639523</v>
+        <v>7.696408296799376</v>
       </c>
       <c r="D3" t="n">
-        <v>6.058105013700082</v>
+        <v>8.192476229979162</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89653242199991</v>
+        <v>18.50734262056691</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.370260371152803</v>
+        <v>1.118906780390412</v>
       </c>
       <c r="C4" t="n">
-        <v>5.0062585241997</v>
+        <v>4.442158327291593</v>
       </c>
       <c r="D4" t="n">
-        <v>6.370832941682186</v>
+        <v>5.787000140268424</v>
       </c>
       <c r="E4" t="n">
-        <v>12.74735183703469</v>
+        <v>11.34806524795043</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.528178664797597</v>
+        <v>1.242679663214612</v>
       </c>
       <c r="C5" t="n">
-        <v>5.531500392549645</v>
+        <v>4.986373177978734</v>
       </c>
       <c r="D5" t="n">
-        <v>6.74184801835698</v>
+        <v>6.074438384631311</v>
       </c>
       <c r="E5" t="n">
-        <v>13.80152707570422</v>
+        <v>12.30349122582466</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.709102092372582</v>
+        <v>1.375834561149217</v>
       </c>
       <c r="C6" t="n">
-        <v>6.196346076127521</v>
+        <v>5.700100206274184</v>
       </c>
       <c r="D6" t="n">
-        <v>7.178756306144038</v>
+        <v>6.455320626060483</v>
       </c>
       <c r="E6" t="n">
-        <v>15.08420447464414</v>
+        <v>13.53125539348388</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.912105928031676</v>
+        <v>1.510992544330475</v>
       </c>
       <c r="C7" t="n">
-        <v>6.985735155778724</v>
+        <v>6.550115485222739</v>
       </c>
       <c r="D7" t="n">
-        <v>7.646333618828572</v>
+        <v>6.795370704375395</v>
       </c>
       <c r="E7" t="n">
-        <v>16.54417470263897</v>
+        <v>14.85647873392861</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.151750244036773</v>
+        <v>1.658822239225255</v>
       </c>
       <c r="C8" t="n">
-        <v>4.679037462404898</v>
+        <v>7.535118664756801</v>
       </c>
       <c r="D8" t="n">
-        <v>5.940221440300684</v>
+        <v>7.249993869053919</v>
       </c>
       <c r="E8" t="n">
-        <v>11.77100914674235</v>
+        <v>16.44393477303597</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.432870871693193</v>
+        <v>1.815605897920335</v>
       </c>
       <c r="C9" t="n">
-        <v>5.707449632761601</v>
+        <v>8.672058079361728</v>
       </c>
       <c r="D9" t="n">
-        <v>6.622475104282461</v>
+        <v>7.682502842779835</v>
       </c>
       <c r="E9" t="n">
-        <v>13.76279560873725</v>
+        <v>18.1701668200619</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.732525673525589</v>
+        <v>1.132612873958418</v>
       </c>
       <c r="C10" t="n">
-        <v>6.865718873476133</v>
+        <v>6.498944000141908</v>
       </c>
       <c r="D10" t="n">
-        <v>7.256113146975334</v>
+        <v>6.063048019456324</v>
       </c>
       <c r="E10" t="n">
-        <v>15.85435769397706</v>
+        <v>13.69460489355665</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.046200692304561</v>
+        <v>1.079029084260627</v>
       </c>
       <c r="C11" t="n">
-        <v>8.091538219934264</v>
+        <v>6.848671984825749</v>
       </c>
       <c r="D11" t="n">
-        <v>7.907248342839601</v>
+        <v>5.94966597709286</v>
       </c>
       <c r="E11" t="n">
-        <v>18.04498725507843</v>
+        <v>13.87736704617924</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.366741706763884</v>
+        <v>1.181572631969206</v>
       </c>
       <c r="C12" t="n">
-        <v>9.377056087330072</v>
+        <v>8.066461289604621</v>
       </c>
       <c r="D12" t="n">
-        <v>8.529649005514655</v>
+        <v>6.36004633494507</v>
       </c>
       <c r="E12" t="n">
-        <v>20.27344679960861</v>
+        <v>15.6080802565189</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.678193518126936</v>
+        <v>0.9420654620411544</v>
       </c>
       <c r="C13" t="n">
-        <v>10.70000347509128</v>
+        <v>7.661814338345213</v>
       </c>
       <c r="D13" t="n">
-        <v>9.090164065741256</v>
+        <v>5.831375196208161</v>
       </c>
       <c r="E13" t="n">
-        <v>22.46836105895947</v>
+        <v>14.43525499659453</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.550474149316988</v>
+        <v>1.03739316412352</v>
       </c>
       <c r="C14" t="n">
-        <v>7.508838411069475</v>
+        <v>8.957142076805498</v>
       </c>
       <c r="D14" t="n">
-        <v>6.914449081010286</v>
+        <v>6.214178261048078</v>
       </c>
       <c r="E14" t="n">
-        <v>15.97376164139675</v>
+        <v>16.20871350197709</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.587643117399772</v>
+        <v>1.020222396776243</v>
       </c>
       <c r="C15" t="n">
-        <v>7.978958116725103</v>
+        <v>9.658473184288292</v>
       </c>
       <c r="D15" t="n">
-        <v>7.012103525151717</v>
+        <v>6.283548553830157</v>
       </c>
       <c r="E15" t="n">
-        <v>16.57870475927659</v>
+        <v>16.96224413489469</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.847973156134899</v>
+        <v>1.123168461043563</v>
       </c>
       <c r="C16" t="n">
-        <v>9.333819035970912</v>
+        <v>11.27253513240935</v>
       </c>
       <c r="D16" t="n">
-        <v>7.590971424006763</v>
+        <v>6.729095114448487</v>
       </c>
       <c r="E16" t="n">
-        <v>18.77276361611257</v>
+        <v>19.12479870790139</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.485570808589231</v>
+        <v>0.6776808052874882</v>
       </c>
       <c r="C17" t="n">
-        <v>8.573052922473018</v>
+        <v>8.465512278949822</v>
       </c>
       <c r="D17" t="n">
-        <v>7.131464411034043</v>
+        <v>5.612533815454506</v>
       </c>
       <c r="E17" t="n">
-        <v>17.19008814209629</v>
+        <v>14.75572689969182</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.700229944122797</v>
+        <v>0.5348561492736623</v>
       </c>
       <c r="C18" t="n">
-        <v>9.955510769685205</v>
+        <v>7.450286977988195</v>
       </c>
       <c r="D18" t="n">
-        <v>7.715957724234424</v>
+        <v>5.116878852011419</v>
       </c>
       <c r="E18" t="n">
-        <v>19.37169843804243</v>
+        <v>13.10202197927327</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.714200213954229</v>
+        <v>0.6302034863101126</v>
       </c>
       <c r="C19" t="n">
-        <v>10.61033648841783</v>
+        <v>9.214939206463667</v>
       </c>
       <c r="D19" t="n">
-        <v>7.895362299708487</v>
+        <v>5.60260834616457</v>
       </c>
       <c r="E19" t="n">
-        <v>20.21989900208055</v>
+        <v>15.44775103893835</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.919149864692792</v>
+        <v>0.7267878254539137</v>
       </c>
       <c r="C20" t="n">
-        <v>12.2394289938909</v>
+        <v>11.08675901433472</v>
       </c>
       <c r="D20" t="n">
-        <v>8.450020300176806</v>
+        <v>6.100629321574893</v>
       </c>
       <c r="E20" t="n">
-        <v>22.6085991587605</v>
+        <v>17.91417616136353</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.146671501083232</v>
+        <v>0.8136724972797565</v>
       </c>
       <c r="C21" t="n">
-        <v>9.071309517332358</v>
+        <v>13.02722262168671</v>
       </c>
       <c r="D21" t="n">
-        <v>7.092400669882062</v>
+        <v>6.658527089467227</v>
       </c>
       <c r="E21" t="n">
-        <v>17.31038168829765</v>
+        <v>20.49942220843369</v>
       </c>
     </row>
   </sheetData>
